--- a/docs/Kエナジー_DD/チェックシート/PX案件チェックシート_1750_相馬.xlsx
+++ b/docs/Kエナジー_DD/チェックシート/PX案件チェックシート_1750_相馬.xlsx
@@ -2973,7 +2973,7 @@
       <c r="E17" s="9" t="inlineStr"/>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>輸送可否（可／要対策／不可）と必要対策。 / ①幅3m未満の進入路の拡幅要否を確認 ②接続先（中村／駒ヶ嶺）の比較</t>
+          <t>輸送可否（可／要対策／不可）と必要対策。 / ①接続先の比較（中村66kVは空容量3MW、駒ヶ嶺154kVは新駒線増強待ち） ②幅3m未満の進入路の拡幅要否を確認</t>
         </is>
       </c>
     </row>
